--- a/demo/moduon-ai-demo/data/a_telecom_price_2610.xlsx
+++ b/demo/moduon-ai-demo/data/a_telecom_price_2610.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -433,6 +433,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,6 +491,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>리베이트(번호이동)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -517,6 +523,9 @@
       <c r="G5" t="n">
         <v>300000</v>
       </c>
+      <c r="I5" t="n">
+        <v>300000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -544,6 +553,9 @@
       <c r="G6" t="n">
         <v>300000</v>
       </c>
+      <c r="I6" t="n">
+        <v>300000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -571,6 +583,9 @@
       <c r="G7" t="n">
         <v>350000</v>
       </c>
+      <c r="I7" t="n">
+        <v>400000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -603,6 +618,9 @@
           <t>번호이동 지원금 조정(10/1부)</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>250000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -634,6 +652,9 @@
         <is>
           <t>신규 출시</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>450000</v>
       </c>
     </row>
   </sheetData>

--- a/demo/moduon-ai-demo/data/a_telecom_price_2610.xlsx
+++ b/demo/moduon-ai-demo/data/a_telecom_price_2610.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="10월 단가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="10월 정책" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,7 +56,9 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,31 +424,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A통신 2026년 10월 정책 단가표</t>
+          <t>A통신 2026년 10월 단말 정책표</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>※ 대외비 / 금액 단위: 원</t>
+          <t>※ 대외비 / 금액 단위: 출고가는 원, 공시지원금·리베이트는 만원 / 부가서비스 미가입 시 리베이트 5만원 차감</t>
         </is>
       </c>
     </row>
@@ -473,63 +480,86 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>월정액(24개월약정)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>공시지원금(번호이동)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>공시지원금(기기변경)</t>
-        </is>
-      </c>
+          <t>공시지원금</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>리베이트(번호이동)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>리베이트(기기변경)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>비고</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>리베이트(번호이동)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SM-S921N</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>갤S24 256 블랙</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1155000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>69000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>450000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>300000</v>
-      </c>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>115요금제</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89요금제</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>55요금제</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>115요금제</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89요금제</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>55요금제</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>115요금제</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>89요금제</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55요금제</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -538,126 +568,241 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>갤럭시S24 512 블랙</t>
+          <t>갤S24 256 블랙</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1309000</v>
+        <v>1155000</v>
       </c>
       <c r="E6" t="n">
-        <v>69000</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>450000</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>300000</v>
+        <v>25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
       </c>
       <c r="I6" t="n">
-        <v>300000</v>
+        <v>45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" t="n">
+        <v>32</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SM-S926N</t>
+          <t>SM-S921N</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Galaxy S24+ 256GB (BK)</t>
+          <t>갤럭시S24 512 블랙</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1353000</v>
+        <v>1309000</v>
       </c>
       <c r="E7" t="n">
-        <v>690000</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>500000</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>350000</v>
+        <v>25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>400000</v>
+        <v>45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>32</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SM-S926N</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>아이폰16 256 블랙</t>
+          <t>Galaxy S24+ 256GB (BK)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1400000</v>
+        <v>1353000</v>
       </c>
       <c r="E8" t="n">
-        <v>89000</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>200000</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>번호이동 지원금 조정(10/1부)</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H8" t="n">
+        <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>250000</v>
+        <v>50</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35</v>
+      </c>
+      <c r="K8" t="n">
+        <v>45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>350000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>아이폰16 256 블랙</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>38</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>28</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>115요금제 공시지원금 조정(10/1부)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>5</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>SM-F741N</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>갤럭시 Z플립6 256 실버</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>1485000</v>
       </c>
-      <c r="E9" t="n">
-        <v>89000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G9" t="n">
-        <v>250000</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L10" t="n">
+        <v>40</v>
+      </c>
+      <c r="M10" t="n">
+        <v>28</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>신규 출시</t>
         </is>
-      </c>
-      <c r="I9" t="n">
-        <v>450000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="E4:G4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>